--- a/outputs/02_財務モデル.xlsx
+++ b/outputs/02_財務モデル.xlsx
@@ -20,11 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;倍&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,8 +124,15 @@
       <color rgb="FFc00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -173,6 +182,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFc6efce"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -328,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -643,6 +664,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3112,7 +3142,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.005" bestFit="1" customWidth="1" style="37" min="1" max="1"/>
@@ -3124,6 +3154,9 @@
     <col width="10.005" bestFit="1" customWidth="1" style="40" min="7" max="7"/>
     <col width="30.005" bestFit="1" customWidth="1" style="38" min="8" max="8"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="38" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -3144,7 +3177,7 @@
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>※ Solafune以外の9社は「分布の形」を示す例示（仮・要検証）。ただし勝ち馬B＝Humanity Brain（防衛装備庁採択の認知戦AI）は実在候補。黄=入力／回収=投下×MOIC。H列=候補領域・I列=倍率根拠（領域→MOICの橋）。Solafune回収はリターン!B12連動、投下は前提!B18連動。</t>
+          <t>※ Solafune以外の9社は「分布の形」を示す例示（仮・要検証）。ただし勝ち馬B＝Humanity Brain（防衛装備庁採択の認知戦AI）は実在候補。黄=入力／回収F=想定comp倍率(J)×想定Exit売上(K)×想定Exit持分(L)の逆算式、MOIC E=F/D。H列=候補領域・I列=倍率根拠（領域→comp→MOICの橋）。Solafune行はリターン!B12連動（全チェーン駆動）、投下は前提!B18連動。</t>
         </is>
       </c>
       <c r="B2" s="38" t="n"/>
@@ -3213,6 +3246,21 @@
           <t>倍率根拠（TAM/Exit comp）</t>
         </is>
       </c>
+      <c r="J4" s="108" t="inlineStr">
+        <is>
+          <t>想定comp倍率(仮)</t>
+        </is>
+      </c>
+      <c r="K4" s="108" t="inlineStr">
+        <is>
+          <t>想定Exit売上(億,仮)</t>
+        </is>
+      </c>
+      <c r="L4" s="108" t="inlineStr">
+        <is>
+          <t>想定Exit持分%(仮)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="12" t="n">
@@ -3254,6 +3302,11 @@
           <t>EV/Sales17倍×Exit売上101億（§5統計導出）＝206億</t>
         </is>
       </c>
+      <c r="J5" s="109" t="inlineStr">
+        <is>
+          <t>←リターン連動</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="17" t="n">
@@ -3272,11 +3325,12 @@
       <c r="D6" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="19" t="n">
-        <v>8.5</v>
+      <c r="E6" s="19">
+        <f>F6/D6</f>
+        <v/>
       </c>
       <c r="F6" s="19">
-        <f>D6*E6</f>
+        <f>J6*K6*L6</f>
         <v/>
       </c>
       <c r="G6" s="20">
@@ -3290,8 +3344,17 @@
       </c>
       <c r="I6" s="38" t="inlineStr">
         <is>
-          <t>認知ドメインの解析レイヤー＝Solafune(物理GEOINT)の隣接。防衛装備庁採択＝政府アンカー、デュアルユース・ソフト層で天井高→7-8X級。ただしcomps/Exit薄く要検証、influence-opsのESG論点も［仮・要検証］</t>
-        </is>
+          <t>認知ドメインの解析レイヤー＝Solafune(物理GEOINT)の隣接。防衛装備庁採択＝政府アンカー、デュアルユース・ソフト層で天井高。comp17倍×想定Exit売上80億×想定持分10%→EV1,360億・回収136億（8.5X級）。comps/Exit薄く要検証、influence-opsのESG論点も［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J6" s="110" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" s="111" t="n">
+        <v>80</v>
+      </c>
+      <c r="L6" s="112" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -3311,11 +3374,12 @@
       <c r="D7" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <v>5</v>
+      <c r="E7" s="23">
+        <f>F7/D7</f>
+        <v/>
       </c>
       <c r="F7" s="24">
-        <f>D7*E7</f>
+        <f>J7*K7*L7</f>
         <v/>
       </c>
       <c r="G7" s="25">
@@ -3329,8 +3393,17 @@
       </c>
       <c r="I7" s="38" t="inlineStr">
         <is>
-          <t>都市鉱山・精錬/リサイクル：CRMA(重要原材料法)追い風・循環経済TAM拡大→3-5X</t>
-        </is>
+          <t>都市鉱山・精錬/リサイクル：CRMA(重要原材料法)追い風・循環経済TAM拡大。comp10倍×想定Exit売上70億×想定持分10%→EV700億・回収70億（5X級）［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J7" s="110" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="111" t="n">
+        <v>70</v>
+      </c>
+      <c r="L7" s="112" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -3350,11 +3423,12 @@
       <c r="D8" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E8" s="23" t="n">
-        <v>3.5</v>
+      <c r="E8" s="23">
+        <f>F8/D8</f>
+        <v/>
       </c>
       <c r="F8" s="24">
-        <f>D8*E8</f>
+        <f>J8*K8*L8</f>
         <v/>
       </c>
       <c r="G8" s="25">
@@ -3368,8 +3442,17 @@
       </c>
       <c r="I8" s="38" t="inlineStr">
         <is>
-          <t>海上物流・港湾ISR監視：防衛ISR予算・経済安保。ハード薄めSaaSで3-5X下限</t>
-        </is>
+          <t>海上物流・港湾ISR監視：防衛ISR予算・経済安保。ハード薄めSaaS。comp8倍×想定Exit売上65億×想定持分9%→EV520億・回収45.5億（3.5X級）［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J8" s="110" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="111" t="n">
+        <v>65</v>
+      </c>
+      <c r="L8" s="112" t="n">
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -3389,11 +3472,12 @@
       <c r="D9" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>2.3</v>
+      <c r="E9" s="23">
+        <f>F9/D9</f>
+        <v/>
       </c>
       <c r="F9" s="24">
-        <f>D9*E9</f>
+        <f>J9*K9*L9</f>
         <v/>
       </c>
       <c r="G9" s="25">
@@ -3407,8 +3491,17 @@
       </c>
       <c r="I9" s="38" t="inlineStr">
         <is>
-          <t>資源インフラ向けセンシング基盤：黎明期・単価不確実→1-2X</t>
-        </is>
+          <t>資源インフラ向けセンシング基盤：黎明期・単価不確実。comp7倍×想定Exit売上57億×想定持分8%→EV399億・回収29.9億（2.3X級）［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J9" s="110" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="111" t="n">
+        <v>57</v>
+      </c>
+      <c r="L9" s="112" t="n">
+        <v>0.07493734335839598</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -3428,11 +3521,12 @@
       <c r="D10" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="23" t="n">
-        <v>1.5</v>
+      <c r="E10" s="23">
+        <f>F10/D10</f>
+        <v/>
       </c>
       <c r="F10" s="24">
-        <f>D10*E10</f>
+        <f>J10*K10*L10</f>
         <v/>
       </c>
       <c r="G10" s="25">
@@ -3446,8 +3540,17 @@
       </c>
       <c r="I10" s="38" t="inlineStr">
         <is>
-          <t>同領域 早期SU：分布の裾（中位回収〜毀損込みで期待値を作る）</t>
-        </is>
+          <t>同領域 早期SU：分布の中位。comp6倍×想定Exit売上45億×想定持分7%→EV270億・回収18億（1.5X級）［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J10" s="110" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="111" t="n">
+        <v>45</v>
+      </c>
+      <c r="L10" s="112" t="n">
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -3467,11 +3570,12 @@
       <c r="D11" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E11" s="23" t="n">
-        <v>1</v>
+      <c r="E11" s="23">
+        <f>F11/D11</f>
+        <v/>
       </c>
       <c r="F11" s="24">
-        <f>D11*E11</f>
+        <f>J11*K11*L11</f>
         <v/>
       </c>
       <c r="G11" s="25">
@@ -3485,8 +3589,17 @@
       </c>
       <c r="I11" s="38" t="inlineStr">
         <is>
-          <t>同領域 早期SU：分布の裾（中位回収〜毀損込みで期待値を作る）</t>
-        </is>
+          <t>同領域 早期SU（元本回収）：comp5倍×想定Exit売上40億×想定持分6%→EV200億・回収11億（1.0X）［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J11" s="110" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="111" t="n">
+        <v>40</v>
+      </c>
+      <c r="L11" s="112" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -3506,11 +3619,12 @@
       <c r="D12" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="23" t="n">
-        <v>0.5</v>
+      <c r="E12" s="23">
+        <f>F12/D12</f>
+        <v/>
       </c>
       <c r="F12" s="24">
-        <f>D12*E12</f>
+        <f>J12*K12*L12</f>
         <v/>
       </c>
       <c r="G12" s="25">
@@ -3524,8 +3638,17 @@
       </c>
       <c r="I12" s="38" t="inlineStr">
         <is>
-          <t>同領域 早期SU：分布の裾（中位回収〜毀損込みで期待値を作る）</t>
-        </is>
+          <t>同領域 早期SU（部分毀損）：comp5倍×想定Exit売上25億×想定持分5%→EV125億・回収5億（0.5X）［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J12" s="110" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="111" t="n">
+        <v>25</v>
+      </c>
+      <c r="L12" s="112" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -3545,11 +3668,12 @@
       <c r="D13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="23" t="n">
-        <v>0.3</v>
+      <c r="E13" s="23">
+        <f>F13/D13</f>
+        <v/>
       </c>
       <c r="F13" s="24">
-        <f>D13*E13</f>
+        <f>J13*K13*L13</f>
         <v/>
       </c>
       <c r="G13" s="25">
@@ -3563,8 +3687,17 @@
       </c>
       <c r="I13" s="38" t="inlineStr">
         <is>
-          <t>同領域 早期SU：分布の裾（中位回収〜毀損込みで期待値を作る）</t>
-        </is>
+          <t>同領域 早期SU（0-1X）：comp4倍×想定Exit売上18億×想定持分5%→EV72億・回収2.7億（0.3X）［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J13" s="110" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="111" t="n">
+        <v>18</v>
+      </c>
+      <c r="L13" s="112" t="n">
+        <v>0.03750000000000001</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -3584,11 +3717,12 @@
       <c r="D14" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="23" t="n">
-        <v>0</v>
+      <c r="E14" s="23">
+        <f>F14/D14</f>
+        <v/>
       </c>
       <c r="F14" s="24">
-        <f>D14*E14</f>
+        <f>J14*K14*L14</f>
         <v/>
       </c>
       <c r="G14" s="25">
@@ -3602,8 +3736,17 @@
       </c>
       <c r="I14" s="38" t="inlineStr">
         <is>
-          <t>同領域 早期SU：分布の裾（中位回収〜毀損込みで期待値を作る）</t>
-        </is>
+          <t>同領域 早期SU（全損）：想定Exit持分0%（希薄化/毀損で消滅）→回収0億。分布の裾で期待値を作る［仮・要検証］</t>
+        </is>
+      </c>
+      <c r="J14" s="110" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="111" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" s="112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
